--- a/Requirement/import_ready_v5_styled.xlsx
+++ b/Requirement/import_ready_v5_styled.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nastmohaapple/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF4BA84-266C-8341-A1A2-A9F20FB347CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689CA968-BE70-2641-B76E-DD9D708CBFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="80" yWindow="620" windowWidth="33520" windowHeight="18780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
